--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,25 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,6 +561,25 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,6 +599,25 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,25 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,25 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,6 +656,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +675,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,6 +713,25 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,25 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,6 +751,25 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,6 +770,25 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,25 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,25 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,25 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,6 +846,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,6 +865,25 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,25 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,25 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>100</v>
       </c>
     </row>
